--- a/www/download/IND.capital_depreciation.s.us.WIOD13.xlsx
+++ b/www/download/IND.capital_depreciation.s.us.WIOD13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>73994.6418094683</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79181.1389869402</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>85075.6735608099</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>75798.7304682542</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>93309.6043957579</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81386.1847019027</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73240.2575688386</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76571.176634058</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>90593.1774414548</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>106631.113277032</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>117431.073956829</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121290.29491077</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139001.140356346</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>156068.966265597</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>153820.56769653</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,67 +775,67 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59905.1944367106</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58979.3238179988</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52914.4784816549</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53734.4415345215</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>49279.8111499762</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46677.1786338813</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46164.5574335721</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48650.1992998487</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58397.3686997921</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65966.6454507814</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67161.0479808406</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69305.3735133582</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76423.5171545305</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -847,7 +852,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62222.717238969</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>61422.0419641718</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54932.4553463548</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58035.8306529816</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>57184.7261518678</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54091.3048433165</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56030.3001531262</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58895.1190253721</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72794.3248327627</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>85557.9359023419</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>90834.3468905472</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>96526.9172804707</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>109574.060944313</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>124123.390379445</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>119239.864519896</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3443.62463166262</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4051.89129591998</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3523.3172735902</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3364.82099188957</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4304.11149458737</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3191.0931640969</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3618.71202658493</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4152.64652351569</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5156.97902036426</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5890.43529345736</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6687.53934545457</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8066.3175596076</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9923.59892359866</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12848.5149992055</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11756.7165136445</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>176174.148905464</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171676.172847113</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>170998.636500202</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>160959.097885011</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>131041.599210505</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131492.958502162</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118525.207440266</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112010.324850243</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>120347.626048327</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>141591.091309218</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>179114.975053593</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>204569.220881049</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>251726.813290347</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>314488.078124454</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>296150.453867148</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110722.792297013</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>117199.124144212</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>126848.096122143</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>130138.325072029</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>164030.736307941</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>159016.773709937</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>158272.019917835</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>160891.634170375</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>190222.715972857</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>219240.415733455</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>249214.299816807</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>284596.346557063</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>332004.989990302</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>364429.287106666</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>345903.407084287</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>163233.598973876</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>183050.644197672</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>199475.469765096</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>209414.807422265</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>250458.663931067</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>236798.973178692</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>254443.457110566</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>275592.998072507</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>309925.435775457</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>358846.470547436</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>403583.103315396</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>451626.919282066</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>503932.535039312</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>645032.502948187</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>646015.05073943</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,72 +1297,72 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1799.88851864952</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1884.67848454279</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1840.40126977649</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1997.08119499064</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2291.93478452602</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1884.68778117339</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1902.94007258066</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2216.68999777257</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2575.6201023762</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2940.90539275184</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2990.47972834511</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3335.66862591975</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3861.97986126612</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4675.69892152338</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1369,7 +1374,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,67 +1384,67 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19369.6008563163</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21531.1527205147</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19707.8033997415</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20622.5254214358</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>18632.7936569475</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18338.4306873855</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19010.4074538177</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21964.3076817113</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25203.7510737802</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28722.905552541</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30470.7354264256</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32745.0861898034</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37625.375953916</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1456,7 +1461,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,67 +1471,67 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>545218.886890187</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>536270.183370795</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>482928.839595626</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>488629.594542059</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>430224.104651194</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>430296.339159589</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>424668.187026433</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>443543.441700115</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>521138.608556781</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>588923.69268405</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>586517.49466768</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>591775.554255159</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>665486.311066903</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1543,7 +1548,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,67 +1558,67 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43726.5058234011</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42500.2270272354</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37455.5968091088</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37193.7255074607</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>33968.7520381638</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32043.5127684453</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31044.5094679887</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32753.127764187</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38654.3286683495</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43786.9047660551</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43252.9336182844</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44137.7391093515</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49827.6946427098</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1630,7 +1635,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,67 +1645,67 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>111666.839780953</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>117712.649691548</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108465.038102389</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112229.289721988</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>111570.093660555</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110905.937295699</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>113250.316960993</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>126708.424759686</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>163259.66340079</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>192754.613374208</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>207683.404725272</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>225864.713572447</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>267665.349481741</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1717,7 +1722,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>965.288169519933</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1095.15629747023</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1129.11350004515</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1155.65720552426</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1377.25679093992</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1215.3883204992</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1571.473950914</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1514.93878962717</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2033.60220674006</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2513.15929087079</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2519.15435837949</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3114.35149290779</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3917.10466677892</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4272.65347475342</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3778.40567452188</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,67 +1819,67 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29061.5608859837</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25912.6510541753</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23916.2309729482</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23312.6436038033</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>20858.3573202254</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20141.5860883228</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21343.4006245004</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22297.7259075447</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26703.1044921333</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29724.7469496763</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30526.3419559624</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31649.5284130368</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35867.266667186</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1891,7 +1896,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,67 +1906,67 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>368696.272319044</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>374757.016762883</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>335917.698502974</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>342057.503623038</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>318196.133730902</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>303602.466063341</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>303244.161616523</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>325786.728139242</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>391778.055087864</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>446884.949499859</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>467585.74772457</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>495439.844435061</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>568252.242824512</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1978,7 +1983,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,67 +1993,67 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>212499.714423542</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>224850.50712233</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>236980.192946138</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>252738.581404539</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>235405.982950561</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>239573.487447957</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>220660.698319899</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>228590.088732335</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>249010.533575219</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>296735.317653387</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>300360.4609986</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>303542.538328749</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>357449.397718524</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2065,7 +2070,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23297.4316295949</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25967.8266674085</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25494.7645369046</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26345.4417242329</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27930.7465593294</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26068.7347463279</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26185.9150870049</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32221.4677638936</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40148.1042278648</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47959.9744978197</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50736.8265386282</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52637.9684276251</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64642.3039892547</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79446.7654804154</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77932.429363565</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,67 +2167,67 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24281.3112612876</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23641.2683793083</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21697.9329062408</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20663.3372299336</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20521.0982674111</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17197.2226032218</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17023.4952699998</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19329.8830857527</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23389.2251999132</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27383.4672408529</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28520.1577293041</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28261.9257593432</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33446.3359980924</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2239,7 +2244,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48820.455728609</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53897.3708355265</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50959.2593717494</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26748.3570557096</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30790.4912685963</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33924.5517381526</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33006.4345157951</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37126.772629159</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41688.058456389</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49819.1170597574</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51918.1714110241</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67654.7002061312</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79997.4217172849</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>97412.242519939</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>97817.481995248</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79598.9885707496</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81924.8087409971</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83061.1015646558</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79276.1238940516</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>94730.341821083</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91218.9976606844</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>97750.648785807</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102768.893097202</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>120327.821310524</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>138755.049734807</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166112.769596966</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>191272.34521377</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>246937.221100436</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>268399.026185468</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>276516.283674879</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,67 +2428,67 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10488.7768743871</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11033.4416769794</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11134.4807396276</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11315.3345769877</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>13376.253101754</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10874.2771560101</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10630.7815635772</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11640.9397715973</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14520.5981117085</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16629.150595242</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18821.3137148451</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21025.8767361749</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27046.9606938446</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2500,7 +2505,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,67 +2515,67 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>532570.405324964</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.586</t>
+          <t>583658.224533185</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>554401.266081953</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>562859.474626931</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>506053.994820048</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>491120.086991834</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>489277.416315704</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.535</t>
+          <t>533462.561409908</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>648803.876496357</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>732673.078287597</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>754104.806879955</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>783295.026612284</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>894277.088526894</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2587,7 +2592,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.239</t>
+          <t>1226473.32067293</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.136</t>
+          <t>1129566.71870714</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>1049539.1122178</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.992</t>
+          <t>992134.722514214</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.183</t>
+          <t>1093213.36298344</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1313964.23395004</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>1193450.15929933</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>1140530.07417799</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.256</t>
+          <t>1249392.64850755</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.361</t>
+          <t>1354386.78517827</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1.387</t>
+          <t>1380318.97538443</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>1369160.81079135</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1.401</t>
+          <t>1396147.39934067</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1680154.47737408</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.822</t>
+          <t>1832892.07181364</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>145696.578353875</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>157916.283100464</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149880.616669633</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109034.361969183</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>149560.652840448</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>152282.883464335</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>136027.183614188</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>150481.669533285</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166132.54815961</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>179596.344587704</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>207968.219166837</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>234877.971577669</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>254781.297508674</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>247386.29513268</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>222547.759311959</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1395.95483258734</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1580.24346572928</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1848.52760449326</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1952.94932772066</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2106.83762431468</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2107.55554760619</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2353.64683279989</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2656.62558200758</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3254.26837809459</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3851.80935260113</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4434.63563948334</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5078.23561668938</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6476.71319366224</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7819.25595819762</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7166.72546306602</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4175.08094855</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4261.60004968865</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4201.16161449949</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4250.59259583942</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5181.2327738651</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4197.66405646475</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4464.49977975831</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4763.66796561557</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5604.14783772508</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6782.7616790043</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7487.38443913385</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7737.3095113931</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9095.67543161002</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10309.6479930565</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9251.15139886987</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1118.62066777929</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1441.85669541002</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1544.31059508002</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1638.60837739837</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1869.18736365106</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1950.85123539309</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2010.1534933795</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2020.14065163475</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2325.71012261524</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2716.71507882956</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3190.16038166554</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4057.72042495412</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6003.23861011838</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7243.39576346317</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6333.52641786347</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76162.2900437434</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88128.1285321684</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105230.631509148</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>116963.826719313</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>152190.413087539</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>145765.337743674</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149562.358895232</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>141723.884819643</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131535.522973451</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139071.796955236</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>151590.91735484</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>162928.270984153</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171779.798598171</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>185300.614247762</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>166511.613355246</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>932.89922609</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>960.840655929839</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>875.659035093602</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>989.085623425908</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1044.17556978661</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1078.08081156199</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>862.207646516561</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>856.263656253718</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1091.10530276278</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1192.32536178964</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1235.63480864315</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1427.83139407664</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1647.62884320037</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1868.02223162769</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1817.70585291811</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,67 +3211,67 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>110027.566869955</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108739.457365959</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97205.7352092207</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98584.6567466372</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>80799.3798519847</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86116.4171640568</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81697.6068815291</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83929.3014929137</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103415.685580287</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113949.266353193</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114164.356863624</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>119180.940842674</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>131448.962535298</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3283,7 +3288,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,67 +3298,67 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32534.2750404531</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36775.4905979961</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39048.7521164527</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42700.1323934962</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>44835.2815179109</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44103.2692017979</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46811.1494893763</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49827.3965235394</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55762.1077246069</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63770.1575693265</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72637.1060225314</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78486.7579226404</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95281.3014730963</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3370,7 +3375,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,72 +3385,72 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17720.2387145484</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18610.8343067935</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17426.0199046346</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18183.5230660077</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>20647.7903658523</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18163.1608230378</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18466.0667862468</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20517.4658746699</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25308.4632079161</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28993.6147476732</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30153.0258824772</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34444.7574158888</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40434.6222838549</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55496.8585699278</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3457,7 +3462,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8617.41287898989</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9222.91154416165</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9065.44524486267</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10087.1150114193</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10124.3879281573</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9723.90147694129</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10710.8418814459</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11991.5227333167</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15130.2800767773</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18727.5018529183</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23700.9675473141</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29212.0821964871</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39496.4662427948</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46165.9585158812</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39093.442073649</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>60288.685736655</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79310.08058041</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80736.8154033221</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73492.9059206804</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>42521.0574489889</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51458.5746998459</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59017.229562878</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64253.9348439036</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76572.6090534176</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>99462.447220594</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>119659.148141306</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145378.487374225</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>194844.963176684</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>251905.844596173</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226186.665351333</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4828.03350631066</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5694.64809697127</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6121.90301555797</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6880.70630456742</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7178.08752079457</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5681.90994365973</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6816.08576901982</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7709.10601282862</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10010.5117719667</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11667.5714516763</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13425.101268772</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14439.6020682921</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18792.8287519745</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22058.5536337892</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20868.7081725268</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4591.26071040995</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4505.78783777573</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4310.57972243385</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4751.89446529292</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4927.70018155783</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4160.79690153269</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4203.13547048259</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4464.5503937258</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5582.53740291297</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6804.35619968819</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7156.9705791244</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7706.81146613225</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8827.46312789752</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10906.115026677</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7697.2738209167</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,67 +3820,67 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48584.7689935978</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53444.4216949096</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50521.186904373</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52100.602066246</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>58626.1393839092</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53493.4355398349</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48410.5399115568</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51977.8828400502</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62546.5022425303</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64263.2256988064</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65511.8446872189</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67580.784854188</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77034.7308320428</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3892,7 +3897,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50249.0473420036</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54042.2273160281</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57072.2946014152</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>60437.1487229899</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>58926.5023679496</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60800.5712258997</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47302.2703592341</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48553.9364040894</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59459.9517982712</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77482.7485587676</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89064.628388398</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>100631.567739349</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>114239.47159496</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>141094.27536115</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>119011.588844877</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37782.9074514933</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39138.5144894063</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42453.1798851508</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43053.7855929231</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>53470.2346328296</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58497.6052199735</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52945.6614645361</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52379.3049452221</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55356.4598149912</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63808.7762366986</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66818.1184484152</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67761.0261021671</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72993.178344052</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>80237.2057242359</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76754.2698126862</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1398305.05260995</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>1442379.38355156</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1498405.58360455</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.524</t>
+          <t>1525647.58567141</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>1753421.12470311</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.707</t>
+          <t>1708105.88962196</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.748</t>
+          <t>1748357.4301472</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1.736</t>
+          <t>1734047.89120233</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1.753</t>
+          <t>1752117.13337348</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1815800.39005999</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1900400.81906693</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2001458.44541285</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2.112</t>
+          <t>2110117.83727563</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2.255</t>
+          <t>2255303.99835673</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2.308</t>
+          <t>2308172.75375137</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>833569.841043438</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>875488.687222577</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>886984.201130134</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>818259.375990128</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>933812.466595176</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>836645.171300399</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>816787.484410636</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>807605.864811817</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0.901</t>
+          <t>900331.655771199</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.021</t>
+          <t>1020614.7189067</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>1173962.98768064</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1.289</t>
+          <t>1288319.86158487</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>1461269.98597442</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>1414175.90102953</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1299631.73036799</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>6.783</t>
+          <t>6764812.48099371</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>6.922</t>
+          <t>6913405.61643001</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6791329.56333759</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>6.672</t>
+          <t>6679734.30443853</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6.922</t>
+          <t>7089993.60280521</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7.098</t>
+          <t>7099357.48317064</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6.958</t>
+          <t>6951121.01037767</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>7.077</t>
+          <t>7058980.57427049</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>7.851</t>
+          <t>7837602.42785797</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8.707</t>
+          <t>8702874.45314267</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>9.294</t>
+          <t>9289028.18718548</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>9.845</t>
+          <t>9851603.53264219</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>10.986</t>
+          <t>10969600.2737469</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>8.495</t>
+          <t>8488623.54592061</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>8.363</t>
+          <t>8372867.64693806</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>capital_depreciation.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
